--- a/asset/data/parking_log.xlsx
+++ b/asset/data/parking_log.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="11540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="13060" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="parking_log" sheetId="1" state="visible" r:id="rId1"/>
@@ -626,13 +626,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1241,11 +1241,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.3846153846154" defaultRowHeight="16.8"/>
   <cols>
-    <col width="16.9807692307692" customWidth="1" style="3" min="1" max="1"/>
-    <col width="13.6153846153846" customWidth="1" style="3" min="5" max="5"/>
+    <col width="16.9807692307692" customWidth="1" style="1" min="1" max="1"/>
+    <col width="13.6153846153846" customWidth="1" style="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1296,10 +1296,10 @@
           <t>地库 A</t>
         </is>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>0.3230092592592593</v>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="D2" s="2" t="n">
         <v>0.5087152777777778</v>
       </c>
       <c r="E2" s="0" t="n">
@@ -1317,7 +1317,7 @@
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>鄂A·5J182</t>
+          <t>鄂A·8K329</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
@@ -1325,14 +1325,14 @@
           <t>地库 A</t>
         </is>
       </c>
-      <c r="C3" s="1" t="n">
-        <v>0.5404861111111111</v>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>0.6634027777777778</v>
+      <c r="C3" s="2" t="n">
+        <v>0.3266435185185185</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.4830208333333333</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>177</v>
+        <v>225</v>
       </c>
       <c r="F3" s="4" t="n">
         <v>0</v>
@@ -1346,22 +1346,22 @@
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t>鄂A·8K329</t>
+          <t>鄂A·2K165</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>地库 A</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>0.3266435185185185</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>0.4830208333333333</v>
+          <t>地面 D</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>0.3321064814814815</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.5196064814814815</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>225</v>
+        <v>270</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>0</v>
@@ -1375,22 +1375,22 @@
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t>鄂A·8K329</t>
+          <t>鄂A·6Q729</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>地库 A</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>0.582037037037037</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>0.7239930555555556</v>
+          <t>地库 B</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>0.3355208333333333</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.4224305555555555</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>204</v>
+        <v>125</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>0</v>
@@ -1404,22 +1404,22 @@
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t>鄂A·2K165</t>
+          <t>鄂A·1A883</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>地面 D</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>0.3321064814814815</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>0.5196064814814815</v>
+          <t>地库 B</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>0.3406597222222222</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.5364930555555556</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>0</v>
@@ -1433,22 +1433,22 @@
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t>鄂A·6Q729</t>
+          <t>鄂A·5C217</t>
         </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>地库 B</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>0.3355208333333333</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>0.4224305555555555</v>
+          <t>地库 A</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>0.3439583333333333</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.4362152777777778</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>0</v>
@@ -1462,22 +1462,22 @@
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t>鄂A·6Q729</t>
+          <t>鄂A·7D765</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>地库 B</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>0.4273379629629629</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>0.464050925925926</v>
+          <t>地库 A</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>0.3487037037037037</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.4759490740740741</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>53</v>
+        <v>183</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>0</v>
@@ -1491,7 +1491,7 @@
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t>鄂A·6Q729</t>
+          <t>鄂A·4H527</t>
         </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
@@ -1499,14 +1499,14 @@
           <t>地库 B</t>
         </is>
       </c>
-      <c r="C9" s="1" t="n">
-        <v>0.4966898148148148</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>0.6127083333333333</v>
+      <c r="C9" s="2" t="n">
+        <v>0.3530324074074074</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.5056481481481482</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>167</v>
+        <v>220</v>
       </c>
       <c r="F9" s="4" t="n">
         <v>0</v>
@@ -1520,22 +1520,22 @@
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t>鄂A·6Q729</t>
+          <t>鄂A·2P094</t>
         </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>地库 B</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="n">
-        <v>0.6167592592592592</v>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>0.7120601851851852</v>
+          <t>地面 D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>0.3578009259259259</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.5155324074074074</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>137</v>
+        <v>227</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>0</v>
@@ -1549,22 +1549,22 @@
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t>鄂A·1A883</t>
+          <t>鄂A·7M448</t>
         </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>地库 B</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="n">
-        <v>0.3406597222222222</v>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>0.5364930555555556</v>
+          <t>地库 A</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>0.3612847222222222</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.4274652777777778</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>282</v>
+        <v>95</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>0</v>
@@ -1578,7 +1578,7 @@
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t>鄂A·5C217</t>
+          <t>鄂A·3F316</t>
         </is>
       </c>
       <c r="B12" s="0" t="inlineStr">
@@ -1586,14 +1586,14 @@
           <t>地库 A</t>
         </is>
       </c>
-      <c r="C12" s="1" t="n">
-        <v>0.3439583333333333</v>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>0.4362152777777778</v>
+      <c r="C12" s="2" t="n">
+        <v>0.3670486111111111</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.5127083333333333</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>133</v>
+        <v>210</v>
       </c>
       <c r="F12" s="4" t="n">
         <v>0</v>
@@ -1607,22 +1607,22 @@
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t>鄂A·5C217</t>
+          <t>鄂A·0B255</t>
         </is>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>地库 A</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="n">
-        <v>0.4411458333333333</v>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>0.6404861111111111</v>
+          <t>地面 D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>0.3717361111111111</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.4503819444444445</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>287</v>
+        <v>113</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>0</v>
@@ -1636,22 +1636,22 @@
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t>鄂A·7D765</t>
+          <t>鄂A·9X083</t>
         </is>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>地库 A</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="n">
-        <v>0.3487037037037037</v>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>0.4759490740740741</v>
+          <t>地库 B</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>0.3766435185185185</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.4599768518518518</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>183</v>
+        <v>120</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t>鄂A·7D765</t>
+          <t>鄂A·7T032</t>
         </is>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>地库 A</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="n">
-        <v>0.554375</v>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>0.6128819444444444</v>
+          <t>地面 D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>0.3807175925925926</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.4917592592592593</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>84</v>
+        <v>160</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>0</v>
@@ -1694,22 +1694,22 @@
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t>鄂A·7D765</t>
+          <t>鄂A·6Q729</t>
         </is>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>地库 A</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="n">
-        <v>0.675162037037037</v>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>0.6911805555555556</v>
+          <t>地库 B</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>0.4273379629629629</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.464050925925926</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>0</v>
@@ -1723,22 +1723,22 @@
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t>鄂A·4H527</t>
+          <t>鄂A·5C217</t>
         </is>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>地库 B</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="n">
-        <v>0.3530324074074074</v>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>0.5056481481481482</v>
+          <t>地库 A</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>0.4411458333333333</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0.6404861111111111</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>220</v>
+        <v>287</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>0</v>
@@ -1752,22 +1752,22 @@
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t>鄂A·4H527</t>
+          <t>鄂A·0B255</t>
         </is>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>地库 B</t>
-        </is>
-      </c>
-      <c r="C18" s="1" t="n">
-        <v>0.5434375</v>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>0.6287268518518518</v>
+          <t>地面 D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>0.4529861111111111</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.4599768518518518</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>123</v>
+        <v>10</v>
       </c>
       <c r="F18" s="4" t="n">
         <v>0</v>
@@ -1781,22 +1781,22 @@
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t>鄂A·4H527</t>
+          <t>鄂A·0B255</t>
         </is>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>地库 B</t>
-        </is>
-      </c>
-      <c r="C19" s="1" t="n">
-        <v>0.6844097222222222</v>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>0.6980787037037037</v>
+          <t>地面 D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>0.464050925925926</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>0.4932175925925926</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="F19" s="4" t="n">
         <v>0</v>
@@ -1810,19 +1810,19 @@
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t>鄂A·2P094</t>
+          <t>鄂A·9X083</t>
         </is>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>地面 D</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="n">
-        <v>0.3578009259259259</v>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>0.5155324074074074</v>
+          <t>地库 B</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>0.464050925925926</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>0.6217824074074074</v>
       </c>
       <c r="E20" s="0" t="n">
         <v>227</v>
@@ -1839,51 +1839,51 @@
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t>鄂A·7M448</t>
+          <t>鄂A·6T948</t>
         </is>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>地库 A</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="n">
-        <v>0.3612847222222222</v>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>0.4274652777777778</v>
+          <t>C 区（访客）</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>0.4877083333333334</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>0.5712152777777778</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t>包月</t>
+          <t>访客·已缴费</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t>鄂A·7M448</t>
+          <t>鄂A·6Q729</t>
         </is>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>地库 A</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="n">
-        <v>0.5682175925925926</v>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>0.6726041666666667</v>
+          <t>地库 B</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>0.4966898148148148</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>0.6127083333333333</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="F22" s="4" t="n">
         <v>0</v>
@@ -1897,22 +1897,22 @@
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t>鄂A·3F316</t>
+          <t>鄂A·7T032</t>
         </is>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>地库 A</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="n">
-        <v>0.3670486111111111</v>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>0.5127083333333333</v>
+          <t>地面 D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>0.4966898148148148</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>0.7051157407407408</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>210</v>
+        <v>300</v>
       </c>
       <c r="F23" s="4" t="n">
         <v>0</v>
@@ -1934,10 +1934,10 @@
           <t>地库 A</t>
         </is>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>0.5363657407407407</v>
       </c>
-      <c r="D24" s="1" t="n">
+      <c r="D24" s="2" t="n">
         <v>0.7028703703703704</v>
       </c>
       <c r="E24" s="0" t="n">
@@ -1955,22 +1955,22 @@
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t>鄂A·0B255</t>
+          <t>鄂A·5J182</t>
         </is>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>地面 D</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="n">
-        <v>0.3717361111111111</v>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>0.4503819444444445</v>
+          <t>地库 A</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>0.5404861111111111</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>0.6634027777777778</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>113</v>
+        <v>177</v>
       </c>
       <c r="F25" s="4" t="n">
         <v>0</v>
@@ -1984,22 +1984,22 @@
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t>鄂A·0B255</t>
+          <t>鄂A·4H527</t>
         </is>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>地面 D</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="n">
-        <v>0.4529861111111111</v>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>0.4599768518518518</v>
+          <t>地库 B</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>0.5434375</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>0.6287268518518518</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>10</v>
+        <v>123</v>
       </c>
       <c r="F26" s="4" t="n">
         <v>0</v>
@@ -2013,22 +2013,22 @@
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t>鄂A·0B255</t>
+          <t>鄂A·7D765</t>
         </is>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>地面 D</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="n">
-        <v>0.464050925925926</v>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>0.4932175925925926</v>
+          <t>地库 A</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>0.554375</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>0.6128819444444444</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="F27" s="4" t="n">
         <v>0</v>
@@ -2042,22 +2042,22 @@
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t>鄂A·0B255</t>
+          <t>鄂A·7M448</t>
         </is>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>地面 D</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="n">
-        <v>0.6426157407407408</v>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>0.6841203703703703</v>
+          <t>地库 A</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>0.5682175925925926</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>0.6726041666666667</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="F28" s="4" t="n">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     <row r="29">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t>鄂A·9X083</t>
+          <t>鄂A·8K329</t>
         </is>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>地库 B</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="n">
-        <v>0.3766435185185185</v>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>0.4599768518518518</v>
+          <t>地库 A</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>0.582037037037037</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>0.7239930555555556</v>
       </c>
       <c r="E29" s="0" t="n">
-        <v>120</v>
+        <v>204</v>
       </c>
       <c r="F29" s="4" t="n">
         <v>0</v>
@@ -2100,7 +2100,7 @@
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t>鄂A·9X083</t>
+          <t>鄂A·6Q729</t>
         </is>
       </c>
       <c r="B30" s="0" t="inlineStr">
@@ -2108,14 +2108,14 @@
           <t>地库 B</t>
         </is>
       </c>
-      <c r="C30" s="1" t="n">
-        <v>0.464050925925926</v>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>0.6217824074074074</v>
+      <c r="C30" s="2" t="n">
+        <v>0.6167592592592592</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>0.7120601851851852</v>
       </c>
       <c r="E30" s="0" t="n">
-        <v>227</v>
+        <v>137</v>
       </c>
       <c r="F30" s="4" t="n">
         <v>0</v>
@@ -2137,10 +2137,10 @@
           <t>地库 B</t>
         </is>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>0.6265509259259259</v>
       </c>
-      <c r="D31" s="1" t="n">
+      <c r="D31" s="2" t="n">
         <v>0.6587152777777778</v>
       </c>
       <c r="E31" s="0" t="n">
@@ -2158,7 +2158,7 @@
     <row r="32">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t>鄂A·7T032</t>
+          <t>鄂A·0B255</t>
         </is>
       </c>
       <c r="B32" s="0" t="inlineStr">
@@ -2166,14 +2166,14 @@
           <t>地面 D</t>
         </is>
       </c>
-      <c r="C32" s="1" t="n">
-        <v>0.3807175925925926</v>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>0.4917592592592593</v>
+      <c r="C32" s="2" t="n">
+        <v>0.6426157407407408</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>0.6841203703703703</v>
       </c>
       <c r="E32" s="0" t="n">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="F32" s="4" t="n">
         <v>0</v>
@@ -2187,22 +2187,22 @@
     <row r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t>鄂A·7T032</t>
+          <t>鄂A·7D765</t>
         </is>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>地面 D</t>
-        </is>
-      </c>
-      <c r="C33" s="1" t="n">
-        <v>0.4966898148148148</v>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>0.7051157407407408</v>
+          <t>地库 A</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>0.675162037037037</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>0.6911805555555556</v>
       </c>
       <c r="E33" s="0" t="n">
-        <v>300</v>
+        <v>23</v>
       </c>
       <c r="F33" s="4" t="n">
         <v>0</v>
@@ -2216,36 +2216,36 @@
     <row r="34">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t>鄂A·6T948</t>
+          <t>鄂A·4H527</t>
         </is>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>C 区（访客）</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="n">
-        <v>0.4877083333333334</v>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>0.5712152777777778</v>
+          <t>地库 B</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>0.6844097222222222</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>0.6980787037037037</v>
       </c>
       <c r="E34" s="0" t="n">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G34" s="0" t="inlineStr">
         <is>
-          <t>访客·已缴费</t>
+          <t>包月</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>鄂A·3F316</t>
+          <t>鄂A·3K047</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -2254,15 +2254,17 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0.7328009259259259</v>
+        <v>0.7314120370370371</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>0.7676157407407408</v>
+        <v>0.7677430555555556</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="F35" s="5" t="n"/>
+        <v>52</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
           <t>包月</t>
@@ -2272,24 +2274,26 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>鄂A·5C217</t>
+          <t>鄂A·1R365</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>地库 A</t>
+          <t>地库 B</t>
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.7378819444444444</v>
+        <v>0.7377083333333333</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>0.7849305555555556</v>
+        <v>0.7625925925925926</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>67</v>
-      </c>
-      <c r="F36" s="5" t="n"/>
+        <v>36</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
           <t>包月</t>
@@ -2299,24 +2303,26 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>鄂A·4H527</t>
+          <t>鄂A·0D117</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>地库 B</t>
+          <t>地面 D</t>
         </is>
       </c>
       <c r="C37" s="6" t="n">
         <v>0.7419212962962963</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>0.7723842592592592</v>
+        <v>0.7587152777777778</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="F37" s="5" t="n"/>
+        <v>24</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
           <t>包月</t>
@@ -2326,78 +2332,84 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>鄂A·2K165</t>
+          <t>鄂A·8B701</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>地面 D</t>
+          <t>C 区（访客）</t>
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>0.7467361111111112</v>
+        <v>0.7466203703703703</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>0.7587152777777778</v>
+        <v>0.7883564814814815</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="F38" s="5" t="n"/>
+        <v>60</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>10</v>
+      </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>包月</t>
+          <t>访客·已缴费</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>鄂A·1A883</t>
+          <t>鄂A·3Z815</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>地库 B</t>
+          <t>C 区（访客）</t>
         </is>
       </c>
       <c r="C39" s="6" t="n">
-        <v>0.7487037037037036</v>
+        <v>0.7489930555555555</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>0.783587962962963</v>
+        <v>0.7654861111111111</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="F39" s="5" t="n"/>
+        <v>24</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>包月</t>
+          <t>临时·已缴费</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>鄂A·6Q729</t>
+          <t>鄂A·4E201</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>地库 B</t>
+          <t>地库 A</t>
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>0.7538541666666667</v>
+        <v>0.7516435185185185</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>0.779375</v>
+        <v>0.7837152777777778</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="F40" s="5" t="n"/>
+        <v>46</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
           <t>包月</t>
@@ -2407,24 +2419,26 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>鄂A·7D765</t>
+          <t>鄂A·2N708</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>地库 A</t>
+          <t>地库 B</t>
         </is>
       </c>
       <c r="C41" s="6" t="n">
-        <v>0.7585879629629629</v>
+        <v>0.7557175925925926</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>0.7883564814814815</v>
+        <v>0.7931481481481482</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="F41" s="5" t="n"/>
+        <v>54</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
           <t>包月</t>
@@ -2434,24 +2448,26 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>鄂A·7M448</t>
+          <t>鄂A·9F263</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>地库 A</t>
+          <t>地面 D</t>
         </is>
       </c>
       <c r="C42" s="6" t="n">
-        <v>0.7627083333333333</v>
+        <v>0.7585879629629629</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>0.7976041666666667</v>
+        <v>0.779375</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="F42" s="5" t="n"/>
+        <v>30</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
           <t>包月</t>
@@ -2461,24 +2477,26 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>鄂A·8K329</t>
+          <t>鄂A·4Q551</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>地库 A</t>
+          <t>地面 D</t>
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>0.7674537037037037</v>
+        <v>0.7607986111111111</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>0.8071527777777778</v>
+        <v>0.7953935185185185</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="F43" s="5" t="n"/>
+        <v>50</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
           <t>包月</t>
@@ -2488,24 +2506,26 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>鄂A·2P094</t>
+          <t>鄂A·5H632</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>地面 D</t>
+          <t>地库 A</t>
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>0.7698263888888889</v>
+        <v>0.7653703703703704</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>0.781412037037037</v>
+        <v>0.8003819444444444</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="F44" s="5" t="n"/>
+        <v>50</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
           <t>包月</t>
@@ -2515,51 +2535,55 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>鄂A·5J182</t>
+          <t>鄂A·6V339</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>地库 A</t>
+          <t>C 区（访客）</t>
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>0.7745601851851852</v>
+        <v>0.7677430555555556</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>0.8003819444444444</v>
+        <v>0.7973842592592593</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="F45" s="5" t="n"/>
+        <v>43</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>8</v>
+      </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>包月</t>
+          <t>访客·已缴费</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>鄂A·7T032</t>
+          <t>鄂A·6Y884</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>地面 D</t>
+          <t>地库 A</t>
         </is>
       </c>
       <c r="C46" s="6" t="n">
-        <v>0.7765972222222223</v>
+        <v>0.7745138888888888</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>0.7953935185185185</v>
+        <v>0.8045486111111111</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="F46" s="5" t="n"/>
+        <v>43</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
           <t>包月</t>
@@ -2569,24 +2593,26 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>鄂A·0B255</t>
+          <t>鄂A·8W429</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>地面 D</t>
+          <t>地库 B</t>
         </is>
       </c>
       <c r="C47" s="6" t="n">
-        <v>0.7793287037037037</v>
+        <v>0.7792592592592592</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>0.8045486111111111</v>
+        <v>0.8071527777777778</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="F47" s="5" t="n"/>
+        <v>40</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
           <t>包月</t>
@@ -2596,24 +2622,26 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>鄂A·9X083</t>
+          <t>鄂A·7G110</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>地库 B</t>
+          <t>地库 A</t>
         </is>
       </c>
       <c r="C48" s="6" t="n">
         <v>0.783587962962963</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>0.8091203703703703</v>
+        <v>0.8114930555555555</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="F48" s="5" t="n"/>
+        <v>40</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
           <t>包月</t>
@@ -2623,61 +2651,65 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>鄂A·5C217</t>
+          <t>鄂A·5L274</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>地库 A</t>
+          <t>C 区（访客）</t>
         </is>
       </c>
       <c r="C49" s="6" t="n">
-        <v>0.7932638888888889</v>
+        <v>0.7883564814814815</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>0.8112731481481481</v>
+        <v>0.8045486111111111</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="F49" s="5" t="n"/>
+        <v>23</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>包月</t>
+          <t>临时·已缴费</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>鄂A·4H527</t>
+          <t>鄂A·2X046</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>地库 B</t>
+          <t>C 区（访客）</t>
         </is>
       </c>
       <c r="C50" s="6" t="n">
-        <v>0.7955208333333333</v>
+        <v>0.7931481481481482</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>0.8113657407407407</v>
+        <v>0.8071527777777778</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="F50" s="5" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>包月</t>
+          <t>访客·已缴费</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>鄂A·8K329</t>
+          <t>鄂A·4E201</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
@@ -2686,15 +2718,17 @@
         </is>
       </c>
       <c r="C51" s="6" t="n">
-        <v>0.8000925925925926</v>
+        <v>0.7973842592592593</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>0.8114930555555555</v>
+        <v>0.8113657407407407</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="F51" s="5" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
           <t>包月</t>
@@ -2704,7 +2738,7 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>鄂A·3F316</t>
+          <t>鄂A·3K047</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
@@ -2713,16 +2747,47 @@
         </is>
       </c>
       <c r="C52" s="6" t="n">
+        <v>0.8003819444444444</v>
+      </c>
+      <c r="D52" s="6" t="n">
+        <v>0.8114930555555555</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>包月</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>鄂A·1R365</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>地库 B</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="n">
         <v>0.8044212962962963</v>
       </c>
-      <c r="D52" s="6" t="n">
+      <c r="D53" s="6" t="n">
         <v>0.8116203703703704</v>
       </c>
-      <c r="E52" s="5" t="n">
+      <c r="E53" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="F52" s="5" t="n"/>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="F53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>包月</t>
         </is>

--- a/asset/data/parking_log.xlsx
+++ b/asset/data/parking_log.xlsx
@@ -4,11 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="13060"/>
+    <workbookView windowWidth="28800" windowHeight="11540"/>
   </bookViews>
   <sheets>
     <sheet name="parking_log" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">parking_log!$A$1:$A$54</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -1981,7 +1984,7 @@
         <v>8</v>
       </c>
       <c r="C29" s="2">
-        <v>0.582037037037037</v>
+        <v>0.579953703703704</v>
       </c>
       <c r="D29" s="2">
         <v>0.723993055555556</v>
